--- a/output/strava_activities.xlsx
+++ b/output/strava_activities.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP48"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,13 +800,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18750878456</v>
+        <v>18765234837</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46175.13041666667</v>
+        <v>46176.13385416667</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46175.25541666667</v>
+        <v>46176.25885416667</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -856,16 +856,16 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>57.5</v>
+        <v>57.8</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>122.2</v>
+        <v>121.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
@@ -880,16 +880,16 @@
         <v>23.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>19860482229</v>
+        <v>19875070186</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>19860482229</t>
+          <t>19875070186</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1780376196575.fit</t>
+          <t>1780462662492.fit</t>
         </is>
       </c>
       <c r="AK2" t="b">
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
@@ -916,34 +916,34 @@
         <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>30.374759</v>
+        <v>30.37481</v>
       </c>
       <c r="AU2" t="n">
-        <v>30.508728</v>
+        <v>30.50855</v>
       </c>
       <c r="AV2" t="n">
-        <v>30.374811</v>
+        <v>30.374836</v>
       </c>
       <c r="AW2" t="n">
-        <v>30.508761</v>
+        <v>30.508832</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.277</v>
+        <v>10.263</v>
       </c>
       <c r="AY2" t="n">
-        <v>101.45</v>
+        <v>100.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>106.58</v>
+        <v>102.67</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.077</v>
+        <v>6.12</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.456</v>
+        <v>8.694000000000001</v>
       </c>
       <c r="BC2" s="3" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="BD2" t="n">
         <v>2026</v>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="BI2" t="n">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="b">
         <v>1</v>
@@ -1001,34 +1001,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18629572376</v>
+        <v>18750878456</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46166.21927083333</v>
+        <v>46175.13041666667</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46166.34427083333</v>
+        <v>46175.25541666667</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -1073,15 +1073,17 @@
         <v>0</v>
       </c>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>57.5</v>
+      </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>143.1</v>
+        <v>122.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
@@ -1090,22 +1092,22 @@
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>19736833077</v>
+        <v>19860482229</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>19736833077</t>
+          <t>19860482229</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1779601140871.fit</t>
+          <t>1780376196575.fit</t>
         </is>
       </c>
       <c r="AK3" t="b">
@@ -1121,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
@@ -1129,75 +1131,85 @@
         <v>843017438</v>
       </c>
       <c r="AS3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>30.374759</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>30.508728</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>30.374811</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>30.508761</v>
+      </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>10.277</v>
       </c>
       <c r="AY3" t="n">
-        <v>16.75</v>
+        <v>101.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.75</v>
+        <v>106.58</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>6.077</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>8.456</v>
       </c>
       <c r="BC3" s="3" t="n">
-        <v>46166</v>
+        <v>46175</v>
       </c>
       <c r="BD3" t="n">
         <v>2026</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>June</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BK3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr"/>
+      <c r="BM3" t="n">
+        <v>9.869999999999999</v>
+      </c>
       <c r="BN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -1207,34 +1219,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18629572464</v>
+        <v>18629572376</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46166.12425925926</v>
+        <v>46166.21927083333</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46166.24925925926</v>
+        <v>46166.34427083333</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1259,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -1279,17 +1291,15 @@
         <v>0</v>
       </c>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>58.7</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>119</v>
+        <v>143.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
@@ -1298,22 +1308,22 @@
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>19736833135</v>
+        <v>19736833077</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>19736833135</t>
+          <t>19736833077</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1779601141612.fit</t>
+          <t>1779601140871.fit</t>
         </is>
       </c>
       <c r="AK4" t="b">
@@ -1329,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
@@ -1337,34 +1347,26 @@
         <v>843017438</v>
       </c>
       <c r="AS4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>30.374774</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>30.508734</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>30.374898</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>30.508772</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>12.096</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>117.47</v>
+        <v>16.75</v>
       </c>
       <c r="AZ4" t="n">
-        <v>120</v>
+        <v>16.75</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.178</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.957000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC4" s="3" t="n">
         <v>46166</v>
@@ -1389,7 +1391,7 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BJ4" t="n">
         <v>21</v>
@@ -1402,20 +1404,18 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM4" t="n">
-        <v>9.710000000000001</v>
-      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -1425,34 +1425,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18616181767</v>
+        <v>18629572464</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46165.22439814815</v>
+        <v>46166.12425925926</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46165.34939814815</v>
+        <v>46166.24925925926</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1497,15 +1497,17 @@
         <v>0</v>
       </c>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>58.7</v>
+      </c>
       <c r="AA5" t="b">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>129.4</v>
+        <v>119</v>
       </c>
       <c r="AC5" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
@@ -1514,22 +1516,22 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>19723147664</v>
+        <v>19736833135</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>19723147664</t>
+          <t>19736833135</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1779514406022.fit</t>
+          <t>1779601141612.fit</t>
         </is>
       </c>
       <c r="AK5" t="b">
@@ -1545,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
@@ -1553,29 +1555,37 @@
         <v>843017438</v>
       </c>
       <c r="AS5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>30.374774</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>30.508734</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>30.374898</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>30.508772</v>
+      </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>12.096</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.67</v>
+        <v>117.47</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.67</v>
+        <v>120</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>6.178</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>8.957000000000001</v>
       </c>
       <c r="BC5" s="3" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="BD5" t="n">
         <v>2026</v>
@@ -1589,15 +1599,15 @@
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="BI5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BJ5" t="n">
         <v>21</v>
@@ -1610,18 +1620,20 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr"/>
+      <c r="BM5" t="n">
+        <v>9.710000000000001</v>
+      </c>
       <c r="BN5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -1631,34 +1643,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18616181895</v>
+        <v>18616181767</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46165.13488425926</v>
+        <v>46165.22439814815</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46165.25988425926</v>
+        <v>46165.34939814815</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1683,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1703,17 +1715,15 @@
         <v>0</v>
       </c>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
-        <v>57.2</v>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>112.2</v>
+        <v>129.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
@@ -1722,22 +1732,22 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>19723147746</v>
+        <v>19723147664</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>19723147746</t>
+          <t>19723147664</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1779514406728.fit</t>
+          <t>1779514406022.fit</t>
         </is>
       </c>
       <c r="AK6" t="b">
@@ -1753,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
@@ -1761,34 +1771,26 @@
         <v>843017438</v>
       </c>
       <c r="AS6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>30.374766</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>30.50872</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>30.374827</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>30.508902</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>10.405</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>107.12</v>
+        <v>1.67</v>
       </c>
       <c r="AZ6" t="n">
-        <v>108</v>
+        <v>1.67</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.828</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.378</v>
+        <v>0</v>
       </c>
       <c r="BC6" s="3" t="n">
         <v>46165</v>
@@ -1813,7 +1815,7 @@
         </is>
       </c>
       <c r="BI6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BJ6" t="n">
         <v>21</v>
@@ -1826,20 +1828,18 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM6" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -1849,34 +1849,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>18604854789</v>
+        <v>18616181895</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46164.29046296296</v>
+        <v>46165.13488425926</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46164.41546296296</v>
+        <v>46165.25988425926</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1921,15 +1921,17 @@
         <v>0</v>
       </c>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>57.2</v>
+      </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>129.3</v>
+        <v>112.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
@@ -1938,22 +1940,22 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>19711585628</v>
+        <v>19723147746</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19711585628</t>
+          <t>19723147746</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1779434595877.fit</t>
+          <t>1779514406728.fit</t>
         </is>
       </c>
       <c r="AK7" t="b">
@@ -1969,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
@@ -1977,29 +1979,37 @@
         <v>843017438</v>
       </c>
       <c r="AS7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>30.374766</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>30.50872</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>30.374827</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>30.508902</v>
+      </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>10.405</v>
       </c>
       <c r="AY7" t="n">
-        <v>20.92</v>
+        <v>107.12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20.92</v>
+        <v>108</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>5.828</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>9.378</v>
       </c>
       <c r="BC7" s="3" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="BD7" t="n">
         <v>2026</v>
@@ -2013,39 +2023,41 @@
         </is>
       </c>
       <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="BI7" t="n">
         <v>6</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="BI7" t="n">
-        <v>9</v>
       </c>
       <c r="BJ7" t="n">
         <v>21</v>
       </c>
       <c r="BK7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr"/>
+      <c r="BM7" t="n">
+        <v>10.3</v>
+      </c>
       <c r="BN7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -2055,34 +2067,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51.7</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18597799203</v>
+        <v>18604854789</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46163.65184027778</v>
+        <v>46164.29046296296</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46163.77684027778</v>
+        <v>46164.41546296296</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -2107,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -2127,17 +2139,15 @@
         <v>0</v>
       </c>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
-        <v>58.1</v>
-      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>125.8</v>
+        <v>129.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
@@ -2146,22 +2156,22 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>19704399902</v>
+        <v>19711585628</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>19704399902</t>
+          <t>19711585628</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1779383078573.fit</t>
+          <t>1779434595877.fit</t>
         </is>
       </c>
       <c r="AK8" t="b">
@@ -2177,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
@@ -2185,37 +2195,29 @@
         <v>843017438</v>
       </c>
       <c r="AS8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>30.376191</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>30.508426</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>30.376495</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>30.507416</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>8.555999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>83.81999999999999</v>
+        <v>20.92</v>
       </c>
       <c r="AZ8" t="n">
-        <v>83.81999999999999</v>
+        <v>20.92</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.124</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.698</v>
+        <v>0</v>
       </c>
       <c r="BC8" s="3" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BD8" t="n">
         <v>2026</v>
@@ -2229,15 +2231,15 @@
         </is>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="BI8" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BJ8" t="n">
         <v>21</v>
@@ -2247,23 +2249,21 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.800000000000001</v>
-      </c>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -2273,34 +2273,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>51.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>18596369476</v>
+        <v>18597799203</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46161.18721064815</v>
+        <v>46163.65184027778</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46161.31221064815</v>
+        <v>46163.77684027778</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -2345,15 +2345,17 @@
         <v>0</v>
       </c>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>58.1</v>
+      </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>132.9</v>
+        <v>125.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -2362,22 +2364,22 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>19702940792</v>
+        <v>19704399902</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19702940792</t>
+          <t>19704399902</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1779376437995.fit</t>
+          <t>1779383078573.fit</t>
         </is>
       </c>
       <c r="AK9" t="b">
@@ -2393,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
@@ -2401,29 +2403,37 @@
         <v>843017438</v>
       </c>
       <c r="AS9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>30.376191</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>30.508426</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>30.376495</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>30.507416</v>
+      </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>8.555999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>15.25</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.25</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>6.124</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>8.698</v>
       </c>
       <c r="BC9" s="3" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="BD9" t="n">
         <v>2026</v>
@@ -2437,15 +2447,15 @@
         </is>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="BI9" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BJ9" t="n">
         <v>21</v>
@@ -2455,21 +2465,23 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>Morning</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr"/>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="BN9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -2479,34 +2491,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18596369726</v>
+        <v>18596369476</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46161.12844907407</v>
+        <v>46161.18721064815</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46161.25344907407</v>
+        <v>46161.31221064815</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2531,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -2551,17 +2563,15 @@
         <v>0</v>
       </c>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="n">
-        <v>56.7</v>
-      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>111.9</v>
+        <v>132.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
@@ -2570,22 +2580,22 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>19702940940</v>
+        <v>19702940792</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>19702940940</t>
+          <t>19702940792</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1779376438575.fit</t>
+          <t>1779376437995.fit</t>
         </is>
       </c>
       <c r="AK10" t="b">
@@ -2601,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
@@ -2609,34 +2619,26 @@
         <v>843017438</v>
       </c>
       <c r="AS10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>30.374928</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>30.508395</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>30.374849</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>30.508828</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>6.219</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>63.83</v>
+        <v>15.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>65.97</v>
+        <v>15.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.846</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.464</v>
+        <v>0</v>
       </c>
       <c r="BC10" s="3" t="n">
         <v>46161</v>
@@ -2661,7 +2663,7 @@
         </is>
       </c>
       <c r="BI10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BJ10" t="n">
         <v>21</v>
@@ -2674,20 +2676,18 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM10" t="n">
-        <v>10.26</v>
-      </c>
+      <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -2697,34 +2697,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18550690189</v>
+        <v>18596369726</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46160.21092592592</v>
+        <v>46161.12844907407</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46160.33592592592</v>
+        <v>46161.25344907407</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -2769,15 +2769,17 @@
         <v>0</v>
       </c>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>56.7</v>
+      </c>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>132.7</v>
+        <v>111.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
@@ -2786,22 +2788,22 @@
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>19656749417</v>
+        <v>19702940940</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>19656749417</t>
+          <t>19702940940</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1779081437375.fit</t>
+          <t>1779376438575.fit</t>
         </is>
       </c>
       <c r="AK11" t="b">
@@ -2817,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
@@ -2825,29 +2827,37 @@
         <v>843017438</v>
       </c>
       <c r="AS11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>30.374928</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>30.508395</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>30.374849</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>30.508828</v>
+      </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>6.219</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>63.83</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11.5</v>
+        <v>65.97</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>5.846</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>8.464</v>
       </c>
       <c r="BC11" s="3" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="BD11" t="n">
         <v>2026</v>
@@ -2861,15 +2871,15 @@
         </is>
       </c>
       <c r="BG11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="BI11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BJ11" t="n">
         <v>21</v>
@@ -2882,18 +2892,20 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr"/>
+      <c r="BM11" t="n">
+        <v>10.26</v>
+      </c>
       <c r="BN11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -2903,34 +2915,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18550582835</v>
+        <v>18550690189</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46160.12824074074</v>
+        <v>46160.21092592592</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46160.25324074074</v>
+        <v>46160.33592592592</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2955,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -2975,17 +2987,15 @@
         <v>0</v>
       </c>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="n">
-        <v>57.2</v>
-      </c>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>113.4</v>
+        <v>132.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
@@ -2994,22 +3004,22 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>19656640346</v>
+        <v>19656749417</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>19656640346</t>
+          <t>19656749417</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1779079964850.fit</t>
+          <t>1779081437375.fit</t>
         </is>
       </c>
       <c r="AK12" t="b">
@@ -3025,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
@@ -3033,34 +3043,26 @@
         <v>843017438</v>
       </c>
       <c r="AS12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>30.374789</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>30.508699</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>30.37498</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>30.508713</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>10.359</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>104.32</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>105.83</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.958</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.571999999999999</v>
+        <v>0</v>
       </c>
       <c r="BC12" s="3" t="n">
         <v>46160</v>
@@ -3085,7 +3087,7 @@
         </is>
       </c>
       <c r="BI12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BJ12" t="n">
         <v>21</v>
@@ -3098,20 +3100,18 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM12" t="n">
-        <v>10.07</v>
-      </c>
+      <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79.8</v>
+        <v>79.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3138,13 +3138,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18537592801</v>
+        <v>18550582835</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46159.16248842593</v>
+        <v>46160.12824074074</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46159.28748842593</v>
+        <v>46160.25324074074</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3194,16 +3194,16 @@
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>56.2</v>
+        <v>57.2</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>118.4</v>
+        <v>113.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>23.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>19643448237</v>
+        <v>19656640346</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>19643448237</t>
+          <t>19656640346</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1778997533687.fit</t>
+          <t>1779079964850.fit</t>
         </is>
       </c>
       <c r="AK13" t="b">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
@@ -3254,34 +3254,34 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>30.375003</v>
+        <v>30.374789</v>
       </c>
       <c r="AU13" t="n">
-        <v>30.508294</v>
+        <v>30.508699</v>
       </c>
       <c r="AV13" t="n">
-        <v>30.374819</v>
+        <v>30.37498</v>
       </c>
       <c r="AW13" t="n">
-        <v>30.508775</v>
+        <v>30.508713</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.243</v>
+        <v>10.359</v>
       </c>
       <c r="AY13" t="n">
-        <v>105.98</v>
+        <v>104.32</v>
       </c>
       <c r="AZ13" t="n">
-        <v>107.42</v>
+        <v>105.83</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.8</v>
+        <v>5.958</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.242</v>
+        <v>8.571999999999999</v>
       </c>
       <c r="BC13" s="3" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BD13" t="n">
         <v>2026</v>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="BG13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="BI13" t="n">
         <v>6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BK13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>10.35</v>
+        <v>10.07</v>
       </c>
       <c r="BN13" t="b">
         <v>1</v>
@@ -3339,34 +3339,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>18532981561</v>
+        <v>18537592801</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46158.72967592593</v>
+        <v>46159.16248842593</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46158.85467592593</v>
+        <v>46159.28748842593</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -3411,15 +3411,17 @@
         <v>0</v>
       </c>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>56.2</v>
+      </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>142</v>
+        <v>118.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
@@ -3428,22 +3430,22 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>19638765442</v>
+        <v>19643448237</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>19638765442</t>
+          <t>19643448237</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1778953389002.fit</t>
+          <t>1778997533687.fit</t>
         </is>
       </c>
       <c r="AK14" t="b">
@@ -3459,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
@@ -3467,29 +3469,37 @@
         <v>843017438</v>
       </c>
       <c r="AS14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>30.375003</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>30.508294</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>30.374819</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>30.508775</v>
+      </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>10.243</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.33</v>
+        <v>105.98</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10.33</v>
+        <v>107.42</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>10.242</v>
       </c>
       <c r="BC14" s="3" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="BD14" t="n">
         <v>2026</v>
@@ -3503,15 +3513,15 @@
         </is>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="BI14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BJ14" t="n">
         <v>20</v>
@@ -3521,21 +3531,23 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr"/>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="BM14" t="n">
+        <v>10.35</v>
+      </c>
       <c r="BN14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -3545,34 +3557,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>50.6</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18532825686</v>
+        <v>18532981561</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46158.68059027778</v>
+        <v>46158.72967592593</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46158.80559027778</v>
+        <v>46158.85467592593</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -3597,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -3617,17 +3629,15 @@
         <v>0</v>
       </c>
       <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="n">
-        <v>56.2</v>
-      </c>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>120.5</v>
+        <v>142</v>
       </c>
       <c r="AC15" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
@@ -3636,22 +3646,22 @@
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>19638607626</v>
+        <v>19638765442</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19638607626</t>
+          <t>19638765442</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1778952521129.fit</t>
+          <t>1778953389002.fit</t>
         </is>
       </c>
       <c r="AK15" t="b">
@@ -3667,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
@@ -3675,34 +3685,26 @@
         <v>843017438</v>
       </c>
       <c r="AS15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>30.375016</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>30.508289</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>30.374844</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>30.508729</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="n">
-        <v>6.126</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>63.67</v>
+        <v>10.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>66.42</v>
+        <v>10.33</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.774</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.074999999999999</v>
+        <v>0</v>
       </c>
       <c r="BC15" s="3" t="n">
         <v>46158</v>
@@ -3727,7 +3729,7 @@
         </is>
       </c>
       <c r="BI15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BJ15" t="n">
         <v>20</v>
@@ -3740,20 +3742,18 @@
           <t>Evening</t>
         </is>
       </c>
-      <c r="BM15" t="n">
-        <v>10.39</v>
-      </c>
+      <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85.7</v>
+        <v>50.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18512435348</v>
+        <v>18532825686</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46157.13755787037</v>
+        <v>46158.68059027778</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46157.26255787037</v>
+        <v>46158.80559027778</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3836,16 +3836,16 @@
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>110</v>
+        <v>120.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
@@ -3860,16 +3860,16 @@
         <v>23.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>19618007886</v>
+        <v>19638607626</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>19618007886</t>
+          <t>19638607626</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1778822029377.fit</t>
+          <t>1778952521129.fit</t>
         </is>
       </c>
       <c r="AK16" t="b">
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
@@ -3896,34 +3896,34 @@
         <v>1</v>
       </c>
       <c r="AT16" t="n">
-        <v>30.374961</v>
+        <v>30.375016</v>
       </c>
       <c r="AU16" t="n">
-        <v>30.508325</v>
+        <v>30.508289</v>
       </c>
       <c r="AV16" t="n">
-        <v>30.374812</v>
+        <v>30.374844</v>
       </c>
       <c r="AW16" t="n">
-        <v>30.508838</v>
+        <v>30.508729</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.291</v>
+        <v>6.126</v>
       </c>
       <c r="AY16" t="n">
-        <v>108.73</v>
+        <v>63.67</v>
       </c>
       <c r="AZ16" t="n">
-        <v>109.75</v>
+        <v>66.42</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.677</v>
+        <v>5.774</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.651</v>
+        <v>8.074999999999999</v>
       </c>
       <c r="BC16" s="3" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BD16" t="n">
         <v>2026</v>
@@ -3937,29 +3937,29 @@
         </is>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="BI16" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BJ16" t="n">
         <v>20</v>
       </c>
       <c r="BK16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>10.57</v>
+        <v>10.39</v>
       </c>
       <c r="BN16" t="b">
         <v>1</v>
@@ -3981,34 +3981,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18499180341</v>
+        <v>18512435348</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46156.1831712963</v>
+        <v>46157.13755787037</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46156.3081712963</v>
+        <v>46157.26255787037</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -4053,15 +4053,17 @@
         <v>0</v>
       </c>
       <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>55.8</v>
+      </c>
       <c r="AA17" t="b">
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>136.4</v>
+        <v>110</v>
       </c>
       <c r="AC17" t="n">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
@@ -4070,22 +4072,22 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>19604636969</v>
+        <v>19618007886</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>19604636969</t>
+          <t>19618007886</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1778733584396.fit</t>
+          <t>1778822029377.fit</t>
         </is>
       </c>
       <c r="AK17" t="b">
@@ -4101,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
@@ -4109,29 +4111,37 @@
         <v>843017438</v>
       </c>
       <c r="AS17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>30.374961</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>30.508325</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>30.374812</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>30.508838</v>
+      </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>10.291</v>
       </c>
       <c r="AY17" t="n">
-        <v>13.92</v>
+        <v>108.73</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.92</v>
+        <v>109.75</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>5.677</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>8.651</v>
       </c>
       <c r="BC17" s="3" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="BD17" t="n">
         <v>2026</v>
@@ -4145,15 +4155,15 @@
         </is>
       </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="BI17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BJ17" t="n">
         <v>20</v>
@@ -4166,18 +4176,20 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM17" t="inlineStr"/>
+      <c r="BM17" t="n">
+        <v>10.57</v>
+      </c>
       <c r="BN17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>Zone 3</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -4187,34 +4199,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50.8</v>
+        <v>0</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18499177490</v>
+        <v>18499180341</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46156.12497685185</v>
+        <v>46156.1831712963</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46156.24997685185</v>
+        <v>46156.3081712963</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -4239,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -4259,17 +4271,15 @@
         <v>0</v>
       </c>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
-        <v>54.9</v>
-      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="b">
         <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>108.6</v>
+        <v>136.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
@@ -4278,22 +4288,22 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>19604634102</v>
+        <v>19604636969</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>19604634102</t>
+          <t>19604636969</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1778733536041.fit</t>
+          <t>1778733584396.fit</t>
         </is>
       </c>
       <c r="AK18" t="b">
@@ -4309,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
@@ -4317,34 +4327,26 @@
         <v>843017438</v>
       </c>
       <c r="AS18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>30.374843</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>30.50854</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>30.374825</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>30.50889</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="n">
-        <v>6.147</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>66.2</v>
+        <v>13.92</v>
       </c>
       <c r="AZ18" t="n">
-        <v>68</v>
+        <v>13.92</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.573</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.582</v>
+        <v>0</v>
       </c>
       <c r="BC18" s="3" t="n">
         <v>46156</v>
@@ -4369,7 +4371,7 @@
         </is>
       </c>
       <c r="BI18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BJ18" t="n">
         <v>20</v>
@@ -4382,20 +4384,18 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM18" t="n">
-        <v>10.77</v>
-      </c>
+      <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>Zone 1</t>
+          <t>Zone 3</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>91.8</v>
+        <v>50.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4422,13 +4422,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>18459693248</v>
+        <v>18499177490</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46153.12858796296</v>
+        <v>46156.12497685185</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46153.25358796296</v>
+        <v>46156.24997685185</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>56.6</v>
+        <v>54.9</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>121.5</v>
+        <v>108.6</v>
       </c>
       <c r="AC19" t="n">
         <v>136</v>
@@ -4496,22 +4496,22 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AG19" t="n">
         <v>23.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>19564861624</v>
+        <v>19604634102</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>19564861624</t>
+          <t>19604634102</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1778475869507.fit</t>
+          <t>1778733536041.fit</t>
         </is>
       </c>
       <c r="AK19" t="b">
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr"/>
@@ -4538,34 +4538,34 @@
         <v>1</v>
       </c>
       <c r="AT19" t="n">
-        <v>30.374787</v>
+        <v>30.374843</v>
       </c>
       <c r="AU19" t="n">
-        <v>30.50871</v>
+        <v>30.50854</v>
       </c>
       <c r="AV19" t="n">
-        <v>30.374893</v>
+        <v>30.374825</v>
       </c>
       <c r="AW19" t="n">
-        <v>30.508919</v>
+        <v>30.50889</v>
       </c>
       <c r="AX19" t="n">
-        <v>11.282</v>
+        <v>6.147</v>
       </c>
       <c r="AY19" t="n">
-        <v>115.48</v>
+        <v>66.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.861</v>
+        <v>5.573</v>
       </c>
       <c r="BB19" t="n">
-        <v>17.485</v>
+        <v>7.582</v>
       </c>
       <c r="BC19" s="3" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="BD19" t="n">
         <v>2026</v>
@@ -4579,15 +4579,15 @@
         </is>
       </c>
       <c r="BG19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="BI19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ19" t="n">
         <v>20</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>10.24</v>
+        <v>10.77</v>
       </c>
       <c r="BN19" t="b">
         <v>1</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 1</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4640,13 +4640,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18446925064</v>
+        <v>18459693248</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46152.14229166666</v>
+        <v>46153.12858796296</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46152.26729166666</v>
+        <v>46153.25358796296</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4696,16 +4696,16 @@
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>55.5</v>
+        <v>56.6</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>118.3</v>
+        <v>121.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
@@ -4720,16 +4720,16 @@
         <v>23.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>19551897865</v>
+        <v>19564861624</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>19551897865</t>
+          <t>19564861624</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1778390790919.fit</t>
+          <t>1778475869507.fit</t>
         </is>
       </c>
       <c r="AK20" t="b">
@@ -4756,34 +4756,34 @@
         <v>1</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.375152</v>
+        <v>30.374787</v>
       </c>
       <c r="AU20" t="n">
-        <v>30.508084</v>
+        <v>30.50871</v>
       </c>
       <c r="AV20" t="n">
-        <v>30.374905</v>
+        <v>30.374893</v>
       </c>
       <c r="AW20" t="n">
-        <v>30.50868</v>
+        <v>30.508919</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.226</v>
+        <v>11.282</v>
       </c>
       <c r="AY20" t="n">
-        <v>119</v>
+        <v>115.48</v>
       </c>
       <c r="AZ20" t="n">
-        <v>119.33</v>
+        <v>117</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.659</v>
+        <v>5.861</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.867000000000001</v>
+        <v>17.485</v>
       </c>
       <c r="BC20" s="3" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="BD20" t="n">
         <v>2026</v>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="BG20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="BI20" t="n">
         <v>6</v>
       </c>
       <c r="BJ20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BK20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>10.6</v>
+        <v>10.24</v>
       </c>
       <c r="BN20" t="b">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4858,13 +4858,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18429138499</v>
+        <v>18446925064</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46150.73715277778</v>
+        <v>46152.14229166666</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46150.86215277778</v>
+        <v>46152.26729166666</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4914,16 +4914,16 @@
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>48.9</v>
+        <v>55.5</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.40000000000001</v>
+        <v>118.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
@@ -4932,22 +4932,22 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>50.3</v>
+        <v>41</v>
       </c>
       <c r="AG21" t="n">
-        <v>34.1</v>
+        <v>23.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>19533885300</v>
+        <v>19551897865</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>19533885300</t>
+          <t>19551897865</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1778266268351.fit</t>
+          <t>1778390790919.fit</t>
         </is>
       </c>
       <c r="AK21" t="b">
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
@@ -4974,34 +4974,34 @@
         <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.374722</v>
+        <v>30.375152</v>
       </c>
       <c r="AU21" t="n">
-        <v>30.508739</v>
+        <v>30.508084</v>
       </c>
       <c r="AV21" t="n">
-        <v>30.374893</v>
+        <v>30.374905</v>
       </c>
       <c r="AW21" t="n">
-        <v>30.508794</v>
+        <v>30.50868</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.699</v>
+        <v>11.226</v>
       </c>
       <c r="AY21" t="n">
-        <v>63.42</v>
+        <v>119</v>
       </c>
       <c r="AZ21" t="n">
-        <v>67.42</v>
+        <v>119.33</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.446</v>
+        <v>5.659</v>
       </c>
       <c r="BB21" t="n">
-        <v>18.778</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="BC21" s="3" t="n">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="BD21" t="n">
         <v>2026</v>
@@ -5015,41 +5015,41 @@
         </is>
       </c>
       <c r="BG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="BI21" t="n">
         <v>6</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="BI21" t="n">
-        <v>20</v>
       </c>
       <c r="BJ21" t="n">
         <v>19</v>
       </c>
       <c r="BK21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>13.5</v>
+        <v>10.6</v>
       </c>
       <c r="BN21" t="b">
         <v>1</v>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>Zone 1</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>82</v>
+        <v>38.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>18420963385</v>
+        <v>18429138499</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46150.13748842593</v>
+        <v>46150.73715277778</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>46150.26248842593</v>
+        <v>46150.86215277778</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5132,16 +5132,16 @@
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>56.5</v>
+        <v>48.9</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>113.9</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
@@ -5150,22 +5150,22 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>40</v>
+        <v>50.3</v>
       </c>
       <c r="AG22" t="n">
-        <v>23.1</v>
+        <v>34.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>19525640781</v>
+        <v>19533885300</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>19525640781</t>
+          <t>19533885300</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1778217863135.fit</t>
+          <t>1778266268351.fit</t>
         </is>
       </c>
       <c r="AK22" t="b">
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
@@ -5192,31 +5192,31 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.374981</v>
+        <v>30.374722</v>
       </c>
       <c r="AU22" t="n">
-        <v>30.508309</v>
+        <v>30.508739</v>
       </c>
       <c r="AV22" t="n">
-        <v>30.374898</v>
+        <v>30.374893</v>
       </c>
       <c r="AW22" t="n">
-        <v>30.508826</v>
+        <v>30.508794</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.149</v>
+        <v>4.699</v>
       </c>
       <c r="AY22" t="n">
-        <v>104.55</v>
+        <v>63.42</v>
       </c>
       <c r="AZ22" t="n">
-        <v>106.08</v>
+        <v>67.42</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.825</v>
+        <v>4.446</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.974</v>
+        <v>18.778</v>
       </c>
       <c r="BC22" s="3" t="n">
         <v>46150</v>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="BI22" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BJ22" t="n">
         <v>19</v>
@@ -5251,23 +5251,23 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>10.3</v>
+        <v>13.5</v>
       </c>
       <c r="BN22" t="b">
         <v>1</v>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 1</t>
         </is>
       </c>
     </row>
@@ -5277,34 +5277,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>18407903761</v>
+        <v>18420963385</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46149.21474537037</v>
+        <v>46150.13748842593</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46149.33974537037</v>
+        <v>46150.26248842593</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -5349,15 +5349,17 @@
         <v>0</v>
       </c>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>56.5</v>
+      </c>
       <c r="AA23" t="b">
         <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>90.09999999999999</v>
+        <v>113.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
@@ -5366,22 +5368,22 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>19512472737</v>
+        <v>19525640781</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>19512472737</t>
+          <t>19525640781</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1778131354829.fit</t>
+          <t>1778217863135.fit</t>
         </is>
       </c>
       <c r="AK23" t="b">
@@ -5397,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
@@ -5405,29 +5407,37 @@
         <v>843017438</v>
       </c>
       <c r="AS23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>30.374981</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>30.508309</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>30.374898</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>30.508826</v>
+      </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>10.149</v>
       </c>
       <c r="AY23" t="n">
-        <v>11.25</v>
+        <v>104.55</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11.25</v>
+        <v>106.08</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>5.825</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>7.974</v>
       </c>
       <c r="BC23" s="3" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BD23" t="n">
         <v>2026</v>
@@ -5441,15 +5451,15 @@
         </is>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="BI23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BJ23" t="n">
         <v>19</v>
@@ -5462,18 +5472,20 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM23" t="inlineStr"/>
+      <c r="BM23" t="n">
+        <v>10.3</v>
+      </c>
       <c r="BN23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>Zone 1</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -5483,34 +5495,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>82.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18407819359</v>
+        <v>18407903761</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46149.13516203704</v>
+        <v>46149.21474537037</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46149.26016203704</v>
+        <v>46149.33974537037</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -5535,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
@@ -5555,17 +5567,15 @@
         <v>0</v>
       </c>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="n">
-        <v>54.9</v>
-      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>107.6</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
@@ -5574,22 +5584,22 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>19512387755</v>
+        <v>19512472737</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>19512387755</t>
+          <t>19512472737</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1778130378732.fit</t>
+          <t>1778131354829.fit</t>
         </is>
       </c>
       <c r="AK24" t="b">
@@ -5605,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr"/>
@@ -5613,34 +5623,26 @@
         <v>843017438</v>
       </c>
       <c r="AS24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>30.375032</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>30.508304</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>30.374826</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>30.508769</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="n">
-        <v>10.251</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>109.47</v>
+        <v>11.25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>109.47</v>
+        <v>11.25</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>11.527</v>
+        <v>0</v>
       </c>
       <c r="BC24" s="3" t="n">
         <v>46149</v>
@@ -5665,7 +5667,7 @@
         </is>
       </c>
       <c r="BI24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BJ24" t="n">
         <v>19</v>
@@ -5678,15 +5680,13 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM24" t="n">
-        <v>10.68</v>
-      </c>
+      <c r="BM24" t="inlineStr"/>
       <c r="BN24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>35.9</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5718,13 +5718,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>18400425869</v>
+        <v>18407819359</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46148.14032407408</v>
+        <v>46149.13516203704</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46148.26532407408</v>
+        <v>46149.26016203704</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -5774,16 +5774,16 @@
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>55.3</v>
+        <v>54.9</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>111.9</v>
+        <v>107.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
@@ -5792,22 +5792,22 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>10.1</v>
+        <v>41</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1</v>
+        <v>23.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>19504953990</v>
+        <v>19512387755</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>19504953990</t>
+          <t>19512387755</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>1778081580516.fit</t>
+          <t>1778130378732.fit</t>
         </is>
       </c>
       <c r="AK25" t="b">
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
@@ -5834,34 +5834,34 @@
         <v>1</v>
       </c>
       <c r="AT25" t="n">
-        <v>31.309099</v>
+        <v>30.375032</v>
       </c>
       <c r="AU25" t="n">
-        <v>30.528578</v>
+        <v>30.508304</v>
       </c>
       <c r="AV25" t="n">
-        <v>31.308991</v>
+        <v>30.374826</v>
       </c>
       <c r="AW25" t="n">
-        <v>30.528515</v>
+        <v>30.508769</v>
       </c>
       <c r="AX25" t="n">
-        <v>10.524</v>
+        <v>10.251</v>
       </c>
       <c r="AY25" t="n">
-        <v>110.63</v>
+        <v>109.47</v>
       </c>
       <c r="AZ25" t="n">
-        <v>117.33</v>
+        <v>109.47</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.706</v>
+        <v>5.62</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.208</v>
+        <v>11.527</v>
       </c>
       <c r="BC25" s="3" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="BD25" t="n">
         <v>2026</v>
@@ -5875,11 +5875,11 @@
         </is>
       </c>
       <c r="BG25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="BI25" t="n">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>10.51</v>
+        <v>10.68</v>
       </c>
       <c r="BN25" t="b">
         <v>1</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 1</t>
         </is>
       </c>
     </row>
@@ -5919,34 +5919,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HIIT</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Workout</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HighIntensityIntervalTraining</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>18367714217</v>
+        <v>18400425869</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46146.21745370371</v>
+        <v>46148.14032407408</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46146.34245370371</v>
+        <v>46148.26532407408</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>(GMT+03:00) Africa/Addis_Ababa</t>
+          <t>(GMT+02:00) Africa/Cairo</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -5991,15 +5991,17 @@
         <v>0</v>
       </c>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>55.3</v>
+      </c>
       <c r="AA26" t="b">
         <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>111.6</v>
+        <v>111.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
@@ -6008,22 +6010,22 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH26" t="n">
-        <v>19471981558</v>
+        <v>19504953990</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>19471981558</t>
+          <t>19504953990</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1777872962829.fit</t>
+          <t>1778081580516.fit</t>
         </is>
       </c>
       <c r="AK26" t="b">
@@ -6039,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr"/>
@@ -6047,29 +6049,37 @@
         <v>843017438</v>
       </c>
       <c r="AS26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>31.309099</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>30.528578</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>31.308991</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>30.528515</v>
+      </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>10.524</v>
       </c>
       <c r="AY26" t="n">
-        <v>20.5</v>
+        <v>110.63</v>
       </c>
       <c r="AZ26" t="n">
-        <v>20.5</v>
+        <v>117.33</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>5.706</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>8.208</v>
       </c>
       <c r="BC26" s="3" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="BD26" t="n">
         <v>2026</v>
@@ -6083,15 +6093,15 @@
         </is>
       </c>
       <c r="BG26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="BI26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BJ26" t="n">
         <v>19</v>
@@ -6104,13 +6114,15 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM26" t="inlineStr"/>
+      <c r="BM26" t="n">
+        <v>10.51</v>
+      </c>
       <c r="BN26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>Indoor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
@@ -6125,34 +6137,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>43.6</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Workout</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>HighIntensityIntervalTraining</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>18367592094</v>
+        <v>18367714217</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46146.13516203704</v>
+        <v>46146.21745370371</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46146.26016203704</v>
+        <v>46146.34245370371</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>(GMT+02:00) Africa/Cairo</t>
+          <t>(GMT+03:00) Africa/Addis_Ababa</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -6177,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -6197,17 +6209,15 @@
         <v>0</v>
       </c>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="n">
-        <v>55.6</v>
-      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="b">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>110.2</v>
+        <v>111.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
@@ -6216,22 +6226,22 @@
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>19471857323</v>
+        <v>19471981558</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>19471857323</t>
+          <t>19471981558</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>1777871347202.fit</t>
+          <t>1777872962829.fit</t>
         </is>
       </c>
       <c r="AK27" t="b">
@@ -6247,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
@@ -6255,34 +6265,26 @@
         <v>843017438</v>
       </c>
       <c r="AS27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>31.309082</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>30.528424</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>31.308939</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>30.528704</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="n">
-        <v>10.264</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>107.3</v>
+        <v>20.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>112.17</v>
+        <v>20.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.738</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.237</v>
+        <v>0</v>
       </c>
       <c r="BC27" s="3" t="n">
         <v>46146</v>
@@ -6307,7 +6309,7 @@
         </is>
       </c>
       <c r="BI27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BJ27" t="n">
         <v>19</v>
@@ -6320,15 +6322,13 @@
           <t>Morning</t>
         </is>
       </c>
-      <c r="BM27" t="n">
-        <v>10.45</v>
-      </c>
+      <c r="BM27" t="inlineStr"/>
       <c r="BN27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Indoor</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37.2</v>
+        <v>43.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6360,13 +6360,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>18354164363</v>
+        <v>18367592094</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46145.12824074074</v>
+        <v>46146.13516203704</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46145.25324074074</v>
+        <v>46146.26016203704</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -6416,16 +6416,16 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>110.1</v>
+        <v>110.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
@@ -6440,16 +6440,16 @@
         <v>-1</v>
       </c>
       <c r="AH28" t="n">
-        <v>19458229764</v>
+        <v>19471857323</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>19458229764</t>
+          <t>19471857323</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>1777784481764.fit</t>
+          <t>1777871347202.fit</t>
         </is>
       </c>
       <c r="AK28" t="b">
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr"/>
@@ -6476,34 +6476,34 @@
         <v>1</v>
       </c>
       <c r="AT28" t="n">
-        <v>31.309023</v>
+        <v>31.309082</v>
       </c>
       <c r="AU28" t="n">
-        <v>30.528282</v>
+        <v>30.528424</v>
       </c>
       <c r="AV28" t="n">
-        <v>31.308978</v>
+        <v>31.308939</v>
       </c>
       <c r="AW28" t="n">
-        <v>30.528661</v>
+        <v>30.528704</v>
       </c>
       <c r="AX28" t="n">
-        <v>10.675</v>
+        <v>10.264</v>
       </c>
       <c r="AY28" t="n">
-        <v>113.62</v>
+        <v>107.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>114.42</v>
+        <v>112.17</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.638</v>
+        <v>5.738</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.733</v>
+        <v>8.237</v>
       </c>
       <c r="BC28" s="3" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="BD28" t="n">
         <v>2026</v>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="BG28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="BI28" t="n">
         <v>6</v>
       </c>
       <c r="BJ28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BK28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>10.64</v>
+        <v>10.45</v>
       </c>
       <c r="BN28" t="b">
         <v>1</v>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>55.3</v>
+        <v>37.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6578,13 +6578,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>18340920596</v>
+        <v>18354164363</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46144.12304398148</v>
+        <v>46145.12824074074</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46144.24804398148</v>
+        <v>46145.25324074074</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -6634,16 +6634,16 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>114.5</v>
+        <v>110.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
@@ -6652,22 +6652,22 @@
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="AG29" t="n">
         <v>-1</v>
       </c>
       <c r="AH29" t="n">
-        <v>19444789126</v>
+        <v>19458229764</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>19444789126</t>
+          <t>19458229764</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>1777697648675.fit</t>
+          <t>1777784481764.fit</t>
         </is>
       </c>
       <c r="AK29" t="b">
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
@@ -6694,34 +6694,34 @@
         <v>1</v>
       </c>
       <c r="AT29" t="n">
-        <v>31.30902</v>
+        <v>31.309023</v>
       </c>
       <c r="AU29" t="n">
-        <v>30.528105</v>
+        <v>30.528282</v>
       </c>
       <c r="AV29" t="n">
-        <v>31.309042</v>
+        <v>31.308978</v>
       </c>
       <c r="AW29" t="n">
-        <v>30.52864</v>
+        <v>30.528661</v>
       </c>
       <c r="AX29" t="n">
-        <v>10.665</v>
+        <v>10.675</v>
       </c>
       <c r="AY29" t="n">
-        <v>113.98</v>
+        <v>113.62</v>
       </c>
       <c r="AZ29" t="n">
-        <v>114.67</v>
+        <v>114.42</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.612</v>
+        <v>5.638</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.629</v>
+        <v>7.733</v>
       </c>
       <c r="BC29" s="3" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="BD29" t="n">
         <v>2026</v>
@@ -6735,15 +6735,15 @@
         </is>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="BI29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BJ29" t="n">
         <v>18</v>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>10.69</v>
+        <v>10.64</v>
       </c>
       <c r="BN29" t="b">
         <v>1</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.8</v>
+        <v>55.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6796,13 +6796,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>18327040542</v>
+        <v>18340920596</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46143.1599537037</v>
+        <v>46144.12304398148</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46143.2849537037</v>
+        <v>46144.24804398148</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -6852,16 +6852,16 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>112.7</v>
+        <v>114.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
@@ -6870,22 +6870,22 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.699999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH30" t="n">
-        <v>19430739808</v>
+        <v>19444789126</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>19430739808</t>
+          <t>19444789126</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>1777608670932.fit</t>
+          <t>1777697648675.fit</t>
         </is>
       </c>
       <c r="AK30" t="b">
@@ -6901,7 +6901,7 @@
         <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr"/>
@@ -6912,34 +6912,34 @@
         <v>1</v>
       </c>
       <c r="AT30" t="n">
-        <v>31.309078</v>
+        <v>31.30902</v>
       </c>
       <c r="AU30" t="n">
-        <v>30.528295</v>
+        <v>30.528105</v>
       </c>
       <c r="AV30" t="n">
-        <v>31.298585</v>
+        <v>31.309042</v>
       </c>
       <c r="AW30" t="n">
-        <v>30.521389</v>
+        <v>30.52864</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.696</v>
+        <v>10.665</v>
       </c>
       <c r="AY30" t="n">
-        <v>18.8</v>
+        <v>113.98</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18.8</v>
+        <v>114.67</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.411</v>
+        <v>5.612</v>
       </c>
       <c r="BB30" t="n">
-        <v>7.319</v>
+        <v>8.629</v>
       </c>
       <c r="BC30" s="3" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="BD30" t="n">
         <v>2026</v>
@@ -6953,21 +6953,21 @@
         </is>
       </c>
       <c r="BG30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="BI30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ30" t="n">
         <v>18</v>
       </c>
       <c r="BK30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
@@ -6975,14 +6975,14 @@
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>11.08</v>
+        <v>10.69</v>
       </c>
       <c r="BN30" t="b">
         <v>1</v>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>55.1</v>
+        <v>11.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7014,13 +7014,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18315221581</v>
+        <v>18327040542</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46142.19420138889</v>
+        <v>46143.1599537037</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46142.31920138889</v>
+        <v>46143.2849537037</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -7070,16 +7070,16 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>109.3</v>
+        <v>112.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
@@ -7088,22 +7088,22 @@
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>44.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>19418828072</v>
+        <v>19430739808</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>19418828072</t>
+          <t>19430739808</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>1777529583280.fit</t>
+          <t>1777608670932.fit</t>
         </is>
       </c>
       <c r="AK31" t="b">
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
@@ -7130,56 +7130,56 @@
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>30.37477</v>
+        <v>31.309078</v>
       </c>
       <c r="AU31" t="n">
-        <v>30.508711</v>
+        <v>30.528295</v>
       </c>
       <c r="AV31" t="n">
-        <v>30.374835</v>
+        <v>31.298585</v>
       </c>
       <c r="AW31" t="n">
-        <v>30.508798</v>
+        <v>30.521389</v>
       </c>
       <c r="AX31" t="n">
-        <v>8.092000000000001</v>
+        <v>1.696</v>
       </c>
       <c r="AY31" t="n">
-        <v>88.72</v>
+        <v>18.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>91.08</v>
+        <v>18.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.472</v>
+        <v>5.411</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.61</v>
+        <v>7.319</v>
       </c>
       <c r="BC31" s="3" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="BD31" t="n">
         <v>2026</v>
       </c>
       <c r="BE31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>May</t>
         </is>
       </c>
       <c r="BG31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="BI31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BJ31" t="n">
         <v>18</v>
@@ -7193,14 +7193,14 @@
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>10.96</v>
+        <v>11.08</v>
       </c>
       <c r="BN31" t="b">
         <v>1</v>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68.5</v>
+        <v>55.1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7232,13 +7232,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>18301612169</v>
+        <v>18315221581</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46141.15538194445</v>
+        <v>46142.19420138889</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46141.28038194445</v>
+        <v>46142.31920138889</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -7288,16 +7288,16 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>54.7</v>
+        <v>55.3</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>110.1</v>
+        <v>109.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
@@ -7306,22 +7306,22 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>40</v>
+        <v>44.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>19405118832</v>
+        <v>19418828072</v>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>19405118832</t>
+          <t>19418828072</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1777441082788.fit</t>
+          <t>1777529583280.fit</t>
         </is>
       </c>
       <c r="AK32" t="b">
@@ -7337,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr"/>
@@ -7348,34 +7348,34 @@
         <v>1</v>
       </c>
       <c r="AT32" t="n">
-        <v>30.374776</v>
+        <v>30.37477</v>
       </c>
       <c r="AU32" t="n">
-        <v>30.508694</v>
+        <v>30.508711</v>
       </c>
       <c r="AV32" t="n">
-        <v>30.375006</v>
+        <v>30.374835</v>
       </c>
       <c r="AW32" t="n">
-        <v>30.508913</v>
+        <v>30.508798</v>
       </c>
       <c r="AX32" t="n">
-        <v>10.217</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="AY32" t="n">
-        <v>110.3</v>
+        <v>88.72</v>
       </c>
       <c r="AZ32" t="n">
-        <v>112</v>
+        <v>91.08</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.558</v>
+        <v>5.472</v>
       </c>
       <c r="BB32" t="n">
-        <v>8.053000000000001</v>
+        <v>7.61</v>
       </c>
       <c r="BC32" s="3" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="BD32" t="n">
         <v>2026</v>
@@ -7389,15 +7389,15 @@
         </is>
       </c>
       <c r="BG32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="BI32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BJ32" t="n">
         <v>18</v>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="BM32" t="n">
-        <v>10.8</v>
+        <v>10.96</v>
       </c>
       <c r="BN32" t="b">
         <v>1</v>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>84.5</v>
+        <v>68.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7450,13 +7450,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>18287536551</v>
+        <v>18301612169</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46140.14196759259</v>
+        <v>46141.15538194445</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46140.26696759259</v>
+        <v>46141.28038194445</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -7506,16 +7506,16 @@
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>54.9</v>
+        <v>54.7</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>112.9</v>
+        <v>110.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
@@ -7527,19 +7527,19 @@
         <v>40</v>
       </c>
       <c r="AG33" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="AH33" t="n">
-        <v>19390946924</v>
+        <v>19405118832</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>19390946924</t>
+          <t>19405118832</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1777354831359.fit</t>
+          <t>1777441082788.fit</t>
         </is>
       </c>
       <c r="AK33" t="b">
@@ -7555,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr"/>
@@ -7566,34 +7566,34 @@
         <v>1</v>
       </c>
       <c r="AT33" t="n">
-        <v>30.37509</v>
+        <v>30.374776</v>
       </c>
       <c r="AU33" t="n">
-        <v>30.508229</v>
+        <v>30.508694</v>
       </c>
       <c r="AV33" t="n">
-        <v>30.374861</v>
+        <v>30.375006</v>
       </c>
       <c r="AW33" t="n">
-        <v>30.50883</v>
+        <v>30.508913</v>
       </c>
       <c r="AX33" t="n">
-        <v>10.261</v>
+        <v>10.217</v>
       </c>
       <c r="AY33" t="n">
-        <v>109.45</v>
+        <v>110.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>110.83</v>
+        <v>112</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.623</v>
+        <v>5.558</v>
       </c>
       <c r="BB33" t="n">
-        <v>7.65</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="BC33" s="3" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="BD33" t="n">
         <v>2026</v>
@@ -7607,11 +7607,11 @@
         </is>
       </c>
       <c r="BG33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="BI33" t="n">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="BM33" t="n">
-        <v>10.67</v>
+        <v>10.8</v>
       </c>
       <c r="BN33" t="b">
         <v>1</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>84.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -7668,13 +7668,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>18274374002</v>
+        <v>18287536551</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46139.15075231482</v>
+        <v>46140.14196759259</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46139.27575231482</v>
+        <v>46140.26696759259</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -7724,16 +7724,16 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>55.1</v>
+        <v>54.9</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>113.3</v>
+        <v>112.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
@@ -7742,22 +7742,22 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="AG34" t="n">
         <v>23.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>19377703920</v>
+        <v>19390946924</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>19377703920</t>
+          <t>19390946924</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1777269051424.fit</t>
+          <t>1777354831359.fit</t>
         </is>
       </c>
       <c r="AK34" t="b">
@@ -7773,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="inlineStr"/>
@@ -7784,34 +7784,34 @@
         <v>1</v>
       </c>
       <c r="AT34" t="n">
-        <v>30.374768</v>
+        <v>30.37509</v>
       </c>
       <c r="AU34" t="n">
-        <v>30.508635</v>
+        <v>30.508229</v>
       </c>
       <c r="AV34" t="n">
-        <v>30.374944</v>
+        <v>30.374861</v>
       </c>
       <c r="AW34" t="n">
-        <v>30.508695</v>
+        <v>30.50883</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.981999999999999</v>
+        <v>10.261</v>
       </c>
       <c r="AY34" t="n">
-        <v>106.48</v>
+        <v>109.45</v>
       </c>
       <c r="AZ34" t="n">
-        <v>114.07</v>
+        <v>110.83</v>
       </c>
       <c r="BA34" t="n">
         <v>5.623</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.578</v>
+        <v>7.65</v>
       </c>
       <c r="BC34" s="3" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="BD34" t="n">
         <v>2026</v>
@@ -7825,11 +7825,11 @@
         </is>
       </c>
       <c r="BG34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="BI34" t="n">
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>78.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7886,13 +7886,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18260357219</v>
+        <v>18274374002</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46138.14585648148</v>
+        <v>46139.15075231482</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46138.27085648148</v>
+        <v>46139.27575231482</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -7942,16 +7942,16 @@
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>109.8</v>
+        <v>113.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
@@ -7960,22 +7960,22 @@
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>50</v>
+        <v>39.9</v>
       </c>
       <c r="AG35" t="n">
         <v>23.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>19363500225</v>
+        <v>19377703920</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>19363500225</t>
+          <t>19377703920</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1777183060288.fit</t>
+          <t>1777269051424.fit</t>
         </is>
       </c>
       <c r="AK35" t="b">
@@ -7991,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr"/>
@@ -8002,34 +8002,34 @@
         <v>1</v>
       </c>
       <c r="AT35" t="n">
-        <v>30.374764</v>
+        <v>30.374768</v>
       </c>
       <c r="AU35" t="n">
-        <v>30.508589</v>
+        <v>30.508635</v>
       </c>
       <c r="AV35" t="n">
-        <v>30.374764</v>
+        <v>30.374944</v>
       </c>
       <c r="AW35" t="n">
-        <v>30.508803</v>
+        <v>30.508695</v>
       </c>
       <c r="AX35" t="n">
-        <v>9.484</v>
+        <v>9.981999999999999</v>
       </c>
       <c r="AY35" t="n">
-        <v>102.87</v>
+        <v>106.48</v>
       </c>
       <c r="AZ35" t="n">
-        <v>117.8</v>
+        <v>114.07</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.533</v>
+        <v>5.623</v>
       </c>
       <c r="BB35" t="n">
-        <v>7.351</v>
+        <v>7.578</v>
       </c>
       <c r="BC35" s="3" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="BD35" t="n">
         <v>2026</v>
@@ -8043,21 +8043,21 @@
         </is>
       </c>
       <c r="BG35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="BI35" t="n">
         <v>6</v>
       </c>
       <c r="BJ35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BK35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL35" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="BM35" t="n">
-        <v>10.85</v>
+        <v>10.67</v>
       </c>
       <c r="BN35" t="b">
         <v>1</v>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>66.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8104,13 +8104,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>18246701172</v>
+        <v>18260357219</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46137.14512731481</v>
+        <v>46138.14585648148</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46137.27012731481</v>
+        <v>46138.27085648148</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -8160,16 +8160,16 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>110.7</v>
+        <v>109.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
@@ -8178,22 +8178,22 @@
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AG36" t="n">
         <v>23.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>19349679336</v>
+        <v>19363500225</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>19349679336</t>
+          <t>19363500225</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1777093573628.fit</t>
+          <t>1777183060288.fit</t>
         </is>
       </c>
       <c r="AK36" t="b">
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr"/>
@@ -8220,34 +8220,34 @@
         <v>1</v>
       </c>
       <c r="AT36" t="n">
-        <v>30.374761</v>
+        <v>30.374764</v>
       </c>
       <c r="AU36" t="n">
-        <v>30.508771</v>
+        <v>30.508589</v>
       </c>
       <c r="AV36" t="n">
-        <v>30.374862</v>
+        <v>30.374764</v>
       </c>
       <c r="AW36" t="n">
-        <v>30.50875</v>
+        <v>30.508803</v>
       </c>
       <c r="AX36" t="n">
-        <v>8.343999999999999</v>
+        <v>9.484</v>
       </c>
       <c r="AY36" t="n">
-        <v>91.65000000000001</v>
+        <v>102.87</v>
       </c>
       <c r="AZ36" t="n">
-        <v>94.33</v>
+        <v>117.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.461</v>
+        <v>5.533</v>
       </c>
       <c r="BB36" t="n">
-        <v>7.358</v>
+        <v>7.351</v>
       </c>
       <c r="BC36" s="3" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="BD36" t="n">
         <v>2026</v>
@@ -8261,11 +8261,11 @@
         </is>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="BI36" t="n">
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="BM36" t="n">
-        <v>10.98</v>
+        <v>10.85</v>
       </c>
       <c r="BN36" t="b">
         <v>1</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>74.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8322,13 +8322,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18226045636</v>
+        <v>18246701172</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46135.19142361111</v>
+        <v>46137.14512731481</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46135.27475694445</v>
+        <v>46137.27012731481</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -8378,16 +8378,16 @@
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>111.8</v>
+        <v>110.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
@@ -8402,16 +8402,16 @@
         <v>23.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>19328856893</v>
+        <v>19349679336</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>19328856893</t>
+          <t>19349679336</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1776952952948.fit</t>
+          <t>1777093573628.fit</t>
         </is>
       </c>
       <c r="AK37" t="b">
@@ -8438,34 +8438,34 @@
         <v>1</v>
       </c>
       <c r="AT37" t="n">
-        <v>30.374776</v>
+        <v>30.374761</v>
       </c>
       <c r="AU37" t="n">
-        <v>30.508715</v>
+        <v>30.508771</v>
       </c>
       <c r="AV37" t="n">
-        <v>30.375</v>
+        <v>30.374862</v>
       </c>
       <c r="AW37" t="n">
-        <v>30.508628</v>
+        <v>30.50875</v>
       </c>
       <c r="AX37" t="n">
-        <v>7.917</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="AY37" t="n">
-        <v>86.33</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>88.53</v>
+        <v>94.33</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.501</v>
+        <v>5.461</v>
       </c>
       <c r="BB37" t="n">
-        <v>8.471</v>
+        <v>7.358</v>
       </c>
       <c r="BC37" s="3" t="n">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="BD37" t="n">
         <v>2026</v>
@@ -8479,11 +8479,11 @@
         </is>
       </c>
       <c r="BG37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="BI37" t="n">
@@ -8493,7 +8493,7 @@
         <v>17</v>
       </c>
       <c r="BK37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL37" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="BM37" t="n">
-        <v>10.9</v>
+        <v>10.98</v>
       </c>
       <c r="BN37" t="b">
         <v>1</v>
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -8540,13 +8540,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>18207528243</v>
+        <v>18226045636</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46134.18767361111</v>
+        <v>46135.19142361111</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46134.27100694444</v>
+        <v>46135.27475694445</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -8596,16 +8596,16 @@
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>110.6</v>
+        <v>111.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
@@ -8620,16 +8620,16 @@
         <v>23.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>19310215630</v>
+        <v>19328856893</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>19310215630</t>
+          <t>19328856893</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>1776837720652.fit</t>
+          <t>1776952952948.fit</t>
         </is>
       </c>
       <c r="AK38" t="b">
@@ -8645,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP38" t="inlineStr"/>
       <c r="AQ38" t="inlineStr"/>
@@ -8656,34 +8656,34 @@
         <v>1</v>
       </c>
       <c r="AT38" t="n">
-        <v>30.374789</v>
+        <v>30.374776</v>
       </c>
       <c r="AU38" t="n">
-        <v>30.508725</v>
+        <v>30.508715</v>
       </c>
       <c r="AV38" t="n">
-        <v>30.374822</v>
+        <v>30.375</v>
       </c>
       <c r="AW38" t="n">
-        <v>30.508823</v>
+        <v>30.508628</v>
       </c>
       <c r="AX38" t="n">
-        <v>7.903</v>
+        <v>7.917</v>
       </c>
       <c r="AY38" t="n">
-        <v>86.25</v>
+        <v>86.33</v>
       </c>
       <c r="AZ38" t="n">
-        <v>89.42</v>
+        <v>88.53</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.497</v>
+        <v>5.501</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.556</v>
+        <v>8.471</v>
       </c>
       <c r="BC38" s="3" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="BD38" t="n">
         <v>2026</v>
@@ -8697,11 +8697,11 @@
         </is>
       </c>
       <c r="BG38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="BI38" t="n">
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="BM38" t="n">
-        <v>10.91</v>
+        <v>10.9</v>
       </c>
       <c r="BN38" t="b">
         <v>1</v>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8758,13 +8758,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>18193605475</v>
+        <v>18207528243</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46133.22758101852</v>
+        <v>46134.18767361111</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46133.31091435185</v>
+        <v>46134.27100694444</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -8814,16 +8814,16 @@
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>112.3</v>
+        <v>110.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
@@ -8838,16 +8838,16 @@
         <v>23.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>19296220446</v>
+        <v>19310215630</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>19296220446</t>
+          <t>19310215630</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1776755462648.fit</t>
+          <t>1776837720652.fit</t>
         </is>
       </c>
       <c r="AK39" t="b">
@@ -8874,34 +8874,34 @@
         <v>1</v>
       </c>
       <c r="AT39" t="n">
-        <v>30.374767</v>
+        <v>30.374789</v>
       </c>
       <c r="AU39" t="n">
-        <v>30.508663</v>
+        <v>30.508725</v>
       </c>
       <c r="AV39" t="n">
-        <v>30.375062</v>
+        <v>30.374822</v>
       </c>
       <c r="AW39" t="n">
-        <v>30.508752</v>
+        <v>30.508823</v>
       </c>
       <c r="AX39" t="n">
-        <v>7.358</v>
+        <v>7.903</v>
       </c>
       <c r="AY39" t="n">
-        <v>82.2</v>
+        <v>86.25</v>
       </c>
       <c r="AZ39" t="n">
-        <v>85.38</v>
+        <v>89.42</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.371</v>
+        <v>5.497</v>
       </c>
       <c r="BB39" t="n">
-        <v>7.891</v>
+        <v>7.556</v>
       </c>
       <c r="BC39" s="3" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="BD39" t="n">
         <v>2026</v>
@@ -8915,15 +8915,15 @@
         </is>
       </c>
       <c r="BG39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="BI39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BJ39" t="n">
         <v>17</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="BM39" t="n">
-        <v>11.17</v>
+        <v>10.91</v>
       </c>
       <c r="BN39" t="b">
         <v>1</v>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8976,13 +8976,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>18181454541</v>
+        <v>18193605475</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46132.20015046297</v>
+        <v>46133.22758101852</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46132.28348379629</v>
+        <v>46133.31091435185</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9032,13 +9032,13 @@
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>54.1</v>
+        <v>54.3</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>109.1</v>
+        <v>112.3</v>
       </c>
       <c r="AC40" t="n">
         <v>153</v>
@@ -9050,22 +9050,22 @@
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>49.4</v>
+        <v>40</v>
       </c>
       <c r="AG40" t="n">
         <v>23.1</v>
       </c>
       <c r="AH40" t="n">
-        <v>19284000344</v>
+        <v>19296220446</v>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>19284000344</t>
+          <t>19296220446</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>1776677359043.fit</t>
+          <t>1776755462648.fit</t>
         </is>
       </c>
       <c r="AK40" t="b">
@@ -9081,7 +9081,7 @@
         <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP40" t="inlineStr"/>
       <c r="AQ40" t="inlineStr"/>
@@ -9092,34 +9092,34 @@
         <v>1</v>
       </c>
       <c r="AT40" t="n">
-        <v>30.374609</v>
+        <v>30.374767</v>
       </c>
       <c r="AU40" t="n">
-        <v>30.508889</v>
+        <v>30.508663</v>
       </c>
       <c r="AV40" t="n">
-        <v>30.374871</v>
+        <v>30.375062</v>
       </c>
       <c r="AW40" t="n">
-        <v>30.508839</v>
+        <v>30.508752</v>
       </c>
       <c r="AX40" t="n">
-        <v>6.91</v>
+        <v>7.358</v>
       </c>
       <c r="AY40" t="n">
-        <v>75.87</v>
+        <v>82.2</v>
       </c>
       <c r="AZ40" t="n">
-        <v>100.62</v>
+        <v>85.38</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.465</v>
+        <v>5.371</v>
       </c>
       <c r="BB40" t="n">
-        <v>16.164</v>
+        <v>7.891</v>
       </c>
       <c r="BC40" s="3" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="BD40" t="n">
         <v>2026</v>
@@ -9133,15 +9133,15 @@
         </is>
       </c>
       <c r="BG40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="BI40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BJ40" t="n">
         <v>17</v>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="BM40" t="n">
-        <v>10.98</v>
+        <v>11.17</v>
       </c>
       <c r="BN40" t="b">
         <v>1</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>81</v>
+        <v>67.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9194,13 +9194,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>18166745573</v>
+        <v>18181454541</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46131.21755787037</v>
+        <v>46132.20015046297</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46131.3008912037</v>
+        <v>46132.28348379629</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -9250,16 +9250,16 @@
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>54.8</v>
+        <v>54.1</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>117.6</v>
+        <v>109.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
@@ -9268,22 +9268,22 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="AG41" t="n">
         <v>23.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>19269100973</v>
+        <v>19284000344</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>19269100973</t>
+          <t>19284000344</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>1776581076509.fit</t>
+          <t>1776677359043.fit</t>
         </is>
       </c>
       <c r="AK41" t="b">
@@ -9299,7 +9299,7 @@
         <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP41" t="inlineStr"/>
       <c r="AQ41" t="inlineStr"/>
@@ -9310,34 +9310,34 @@
         <v>1</v>
       </c>
       <c r="AT41" t="n">
-        <v>30.3748</v>
+        <v>30.374609</v>
       </c>
       <c r="AU41" t="n">
-        <v>30.508706</v>
+        <v>30.508889</v>
       </c>
       <c r="AV41" t="n">
-        <v>30.374915</v>
+        <v>30.374871</v>
       </c>
       <c r="AW41" t="n">
-        <v>30.50879</v>
+        <v>30.508839</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.957</v>
+        <v>6.91</v>
       </c>
       <c r="AY41" t="n">
-        <v>74.15000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="AZ41" t="n">
-        <v>89.13</v>
+        <v>100.62</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.63</v>
+        <v>5.465</v>
       </c>
       <c r="BB41" t="n">
-        <v>9.896000000000001</v>
+        <v>16.164</v>
       </c>
       <c r="BC41" s="3" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BD41" t="n">
         <v>2026</v>
@@ -9351,21 +9351,21 @@
         </is>
       </c>
       <c r="BG41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="BI41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BJ41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BK41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL41" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="BM41" t="n">
-        <v>10.66</v>
+        <v>10.98</v>
       </c>
       <c r="BN41" t="b">
         <v>1</v>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9412,13 +9412,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>18129821956</v>
+        <v>18166745573</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46128.44309027777</v>
+        <v>46131.21755787037</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>46128.52642361111</v>
+        <v>46131.3008912037</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -9468,16 +9468,16 @@
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>48.9</v>
+        <v>54.8</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>94.7</v>
+        <v>117.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
@@ -9486,22 +9486,22 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>36.9</v>
+        <v>49.9</v>
       </c>
       <c r="AG42" t="n">
-        <v>35.6</v>
+        <v>23.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>19231831615</v>
+        <v>19269100973</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>19231831615</t>
+          <t>19269100973</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1776336127841.fit</t>
+          <t>1776581076509.fit</t>
         </is>
       </c>
       <c r="AK42" t="b">
@@ -9517,7 +9517,7 @@
         <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
@@ -9528,34 +9528,34 @@
         <v>1</v>
       </c>
       <c r="AT42" t="n">
-        <v>30.37474</v>
+        <v>30.3748</v>
       </c>
       <c r="AU42" t="n">
-        <v>30.508712</v>
+        <v>30.508706</v>
       </c>
       <c r="AV42" t="n">
-        <v>30.37269</v>
+        <v>30.374915</v>
       </c>
       <c r="AW42" t="n">
-        <v>30.510874</v>
+        <v>30.50879</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.355</v>
+        <v>6.957</v>
       </c>
       <c r="AY42" t="n">
-        <v>2</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2</v>
+        <v>89.13</v>
       </c>
       <c r="BA42" t="n">
-        <v>10.638</v>
+        <v>5.63</v>
       </c>
       <c r="BB42" t="n">
-        <v>36.504</v>
+        <v>9.896000000000001</v>
       </c>
       <c r="BC42" s="3" t="n">
-        <v>46128</v>
+        <v>46131</v>
       </c>
       <c r="BD42" t="n">
         <v>2026</v>
@@ -9569,41 +9569,41 @@
         </is>
       </c>
       <c r="BG42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="BI42" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BJ42" t="n">
         <v>16</v>
       </c>
       <c r="BK42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL42" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="BM42" t="n">
-        <v>5.63</v>
+        <v>10.66</v>
       </c>
       <c r="BN42" t="b">
         <v>1</v>
       </c>
       <c r="BO42" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>Zone 1</t>
+          <t>Zone 2</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>61.5</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -9630,13 +9630,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18127971925</v>
+        <v>18129821956</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46128.21991898148</v>
+        <v>46128.44309027777</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46128.30325231481</v>
+        <v>46128.52642361111</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -9686,16 +9686,16 @@
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>54.6</v>
+        <v>48.9</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>116.4</v>
+        <v>94.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
@@ -9704,22 +9704,22 @@
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>45.9</v>
+        <v>36.9</v>
       </c>
       <c r="AG43" t="n">
-        <v>23.1</v>
+        <v>35.6</v>
       </c>
       <c r="AH43" t="n">
-        <v>19229960264</v>
+        <v>19231831615</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>19229960264</t>
+          <t>19231831615</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>1776322072999.fit</t>
+          <t>1776336127841.fit</t>
         </is>
       </c>
       <c r="AK43" t="b">
@@ -9735,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="AO43" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AP43" t="inlineStr"/>
       <c r="AQ43" t="inlineStr"/>
@@ -9746,31 +9746,31 @@
         <v>1</v>
       </c>
       <c r="AT43" t="n">
-        <v>30.374769</v>
+        <v>30.37474</v>
       </c>
       <c r="AU43" t="n">
-        <v>30.508725</v>
+        <v>30.508712</v>
       </c>
       <c r="AV43" t="n">
-        <v>30.374915</v>
+        <v>30.37269</v>
       </c>
       <c r="AW43" t="n">
-        <v>30.508756</v>
+        <v>30.510874</v>
       </c>
       <c r="AX43" t="n">
-        <v>6.153</v>
+        <v>0.355</v>
       </c>
       <c r="AY43" t="n">
-        <v>65.40000000000001</v>
+        <v>2</v>
       </c>
       <c r="AZ43" t="n">
-        <v>88.98</v>
+        <v>2</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.645</v>
+        <v>10.638</v>
       </c>
       <c r="BB43" t="n">
-        <v>13.05</v>
+        <v>36.504</v>
       </c>
       <c r="BC43" s="3" t="n">
         <v>46128</v>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="BI43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BJ43" t="n">
         <v>16</v>
@@ -9805,23 +9805,23 @@
       </c>
       <c r="BL43" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="BM43" t="n">
-        <v>10.63</v>
+        <v>5.63</v>
       </c>
       <c r="BN43" t="b">
         <v>1</v>
       </c>
       <c r="BO43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
-          <t>Zone 2</t>
+          <t>Zone 1</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>52.1</v>
+        <v>61.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -9848,13 +9848,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>18114500626</v>
+        <v>18127971925</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46127.24745370371</v>
+        <v>46128.21991898148</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46127.33078703703</v>
+        <v>46128.30325231481</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -9904,13 +9904,13 @@
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>118.4</v>
+        <v>116.4</v>
       </c>
       <c r="AC44" t="n">
         <v>137</v>
@@ -9922,22 +9922,22 @@
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>42</v>
+        <v>45.9</v>
       </c>
       <c r="AG44" t="n">
         <v>23.1</v>
       </c>
       <c r="AH44" t="n">
-        <v>19216391951</v>
+        <v>19229960264</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>19216391951</t>
+          <t>19229960264</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1776235433957.fit</t>
+          <t>1776322072999.fit</t>
         </is>
       </c>
       <c r="AK44" t="b">
@@ -9953,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="AO44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr"/>
@@ -9964,34 +9964,34 @@
         <v>1</v>
       </c>
       <c r="AT44" t="n">
-        <v>30.374784</v>
+        <v>30.374769</v>
       </c>
       <c r="AU44" t="n">
-        <v>30.508672</v>
+        <v>30.508725</v>
       </c>
       <c r="AV44" t="n">
-        <v>30.372245</v>
+        <v>30.374915</v>
       </c>
       <c r="AW44" t="n">
-        <v>30.499172</v>
+        <v>30.508756</v>
       </c>
       <c r="AX44" t="n">
-        <v>4.148</v>
+        <v>6.153</v>
       </c>
       <c r="AY44" t="n">
-        <v>44.23</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>45.43</v>
+        <v>88.98</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.627</v>
+        <v>5.645</v>
       </c>
       <c r="BB44" t="n">
-        <v>7.686</v>
+        <v>13.05</v>
       </c>
       <c r="BC44" s="3" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="BD44" t="n">
         <v>2026</v>
@@ -10005,11 +10005,11 @@
         </is>
       </c>
       <c r="BG44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="BI44" t="n">
@@ -10027,14 +10027,14 @@
         </is>
       </c>
       <c r="BM44" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="BN44" t="b">
         <v>1</v>
       </c>
       <c r="BO44" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="BP44" t="inlineStr">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>52.1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10066,13 +10066,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>18106961259</v>
+        <v>18114500626</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46126.69180555556</v>
+        <v>46127.24745370371</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46126.77513888889</v>
+        <v>46127.33078703703</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -10122,16 +10122,16 @@
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>52.3</v>
+        <v>54.9</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>111.9</v>
+        <v>118.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
@@ -10140,22 +10140,22 @@
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>38.6</v>
+        <v>42</v>
       </c>
       <c r="AG45" t="n">
-        <v>34.1</v>
+        <v>23.1</v>
       </c>
       <c r="AH45" t="n">
-        <v>19208817757</v>
+        <v>19216391951</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>19208817757</t>
+          <t>19216391951</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1776184958070.fit</t>
+          <t>1776235433957.fit</t>
         </is>
       </c>
       <c r="AK45" t="b">
@@ -10171,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP45" t="inlineStr"/>
       <c r="AQ45" t="inlineStr"/>
@@ -10182,34 +10182,34 @@
         <v>1</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.376706</v>
+        <v>30.374784</v>
       </c>
       <c r="AU45" t="n">
-        <v>30.506363</v>
+        <v>30.508672</v>
       </c>
       <c r="AV45" t="n">
-        <v>30.376662</v>
+        <v>30.372245</v>
       </c>
       <c r="AW45" t="n">
-        <v>30.503674</v>
+        <v>30.499172</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.347</v>
+        <v>4.148</v>
       </c>
       <c r="AY45" t="n">
-        <v>4.38</v>
+        <v>44.23</v>
       </c>
       <c r="AZ45" t="n">
-        <v>4.38</v>
+        <v>45.43</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.745</v>
+        <v>5.627</v>
       </c>
       <c r="BB45" t="n">
-        <v>5.609</v>
+        <v>7.686</v>
       </c>
       <c r="BC45" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="BD45" t="n">
         <v>2026</v>
@@ -10223,15 +10223,15 @@
         </is>
       </c>
       <c r="BG45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="BI45" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BJ45" t="n">
         <v>16</v>
@@ -10241,11 +10241,11 @@
       </c>
       <c r="BL45" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="BM45" t="n">
-        <v>12.62</v>
+        <v>10.66</v>
       </c>
       <c r="BN45" t="b">
         <v>1</v>
@@ -10267,30 +10267,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Outdoor run</t>
+          <t>Outdoor walk</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>44.7</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>18100572666</v>
+        <v>18106961259</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46126.25680555555</v>
+        <v>46126.69180555556</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46126.34013888889</v>
+        <v>46126.77513888889</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10340,16 +10340,16 @@
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>54.7</v>
+        <v>52.3</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>117.5</v>
+        <v>111.9</v>
       </c>
       <c r="AC46" t="n">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
@@ -10358,22 +10358,22 @@
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>42.1</v>
+        <v>38.6</v>
       </c>
       <c r="AG46" t="n">
-        <v>23.1</v>
+        <v>34.1</v>
       </c>
       <c r="AH46" t="n">
-        <v>19202381427</v>
+        <v>19208817757</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>19202381427</t>
+          <t>19208817757</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>1776149374719.fit</t>
+          <t>1776184958070.fit</t>
         </is>
       </c>
       <c r="AK46" t="b">
@@ -10389,7 +10389,7 @@
         <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="inlineStr"/>
       <c r="AQ46" t="inlineStr"/>
@@ -10400,31 +10400,31 @@
         <v>1</v>
       </c>
       <c r="AT46" t="n">
-        <v>30.37474</v>
+        <v>30.376706</v>
       </c>
       <c r="AU46" t="n">
-        <v>30.508674</v>
+        <v>30.506363</v>
       </c>
       <c r="AV46" t="n">
-        <v>30.374879</v>
+        <v>30.376662</v>
       </c>
       <c r="AW46" t="n">
-        <v>30.508827</v>
+        <v>30.503674</v>
       </c>
       <c r="AX46" t="n">
-        <v>3.345</v>
+        <v>0.347</v>
       </c>
       <c r="AY46" t="n">
-        <v>35.22</v>
+        <v>4.38</v>
       </c>
       <c r="AZ46" t="n">
-        <v>38.83</v>
+        <v>4.38</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.699</v>
+        <v>4.745</v>
       </c>
       <c r="BB46" t="n">
-        <v>7.657</v>
+        <v>5.609</v>
       </c>
       <c r="BC46" s="3" t="n">
         <v>46126</v>
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="BI46" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BJ46" t="n">
         <v>16</v>
@@ -10459,11 +10459,11 @@
       </c>
       <c r="BL46" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="BM46" t="n">
-        <v>10.53</v>
+        <v>12.62</v>
       </c>
       <c r="BN46" t="b">
         <v>1</v>
@@ -10485,30 +10485,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Morning Walk</t>
+          <t>Outdoor run</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>34.6</v>
+        <v>44.7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>18087449712</v>
+        <v>18100572666</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46125.22115740741</v>
+        <v>46126.25680555555</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46125.30449074074</v>
+        <v>46126.34013888889</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -10557,35 +10557,41 @@
         <v>0</v>
       </c>
       <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+      <c r="Z47" t="n">
+        <v>54.7</v>
+      </c>
       <c r="AA47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>141</v>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>40</v>
+        <v>42.1</v>
       </c>
       <c r="AG47" t="n">
         <v>23.1</v>
       </c>
       <c r="AH47" t="n">
-        <v>19189190804</v>
+        <v>19202381427</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>19189190804</t>
+          <t>19202381427</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>stripped_7036f6f0-2201-4bb3-b4f7-cb2d51f6f1e9-activity.fit</t>
+          <t>1776149374719.fit</t>
         </is>
       </c>
       <c r="AK47" t="b">
@@ -10600,13 +10606,11 @@
       <c r="AN47" t="b">
         <v>0</v>
       </c>
-      <c r="AO47" t="inlineStr"/>
+      <c r="AO47" t="n">
+        <v>8</v>
+      </c>
       <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>Strava App</t>
-        </is>
-      </c>
+      <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="n">
         <v>843017438</v>
       </c>
@@ -10614,34 +10618,34 @@
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>30.37505</v>
+        <v>30.37474</v>
       </c>
       <c r="AU47" t="n">
-        <v>30.508258</v>
+        <v>30.508674</v>
       </c>
       <c r="AV47" t="n">
-        <v>30.374949</v>
+        <v>30.374879</v>
       </c>
       <c r="AW47" t="n">
-        <v>30.508911</v>
+        <v>30.508827</v>
       </c>
       <c r="AX47" t="n">
-        <v>3.235</v>
+        <v>3.345</v>
       </c>
       <c r="AY47" t="n">
-        <v>34.62</v>
+        <v>35.22</v>
       </c>
       <c r="AZ47" t="n">
-        <v>37.7</v>
+        <v>38.83</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.605</v>
+        <v>5.699</v>
       </c>
       <c r="BB47" t="n">
-        <v>8.712</v>
+        <v>7.657</v>
       </c>
       <c r="BC47" s="3" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="BD47" t="n">
         <v>2026</v>
@@ -10655,15 +10659,15 @@
         </is>
       </c>
       <c r="BG47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="BI47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BJ47" t="n">
         <v>16</v>
@@ -10677,7 +10681,7 @@
         </is>
       </c>
       <c r="BM47" t="n">
-        <v>10.7</v>
+        <v>10.53</v>
       </c>
       <c r="BN47" t="b">
         <v>1</v>
@@ -10687,7 +10691,11 @@
           <t>Short</t>
         </is>
       </c>
-      <c r="BP47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr">
+        <is>
+          <t>Zone 2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -10695,11 +10703,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Outdoor walk</t>
+          <t>Morning Walk</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10712,13 +10720,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>18087447161</v>
+        <v>18087449712</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46125.21821759259</v>
+        <v>46125.22115740741</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46125.30155092593</v>
+        <v>46125.30449074074</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10767,9 +10775,7 @@
         <v>0</v>
       </c>
       <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="n">
-        <v>54.3</v>
-      </c>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="b">
         <v>0</v>
       </c>
@@ -10788,16 +10794,16 @@
         <v>23.1</v>
       </c>
       <c r="AH48" t="n">
-        <v>19189188264</v>
+        <v>19189190804</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>19189188264</t>
+          <t>19189190804</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>stripped_1776059758605.fit</t>
+          <t>stripped_7036f6f0-2201-4bb3-b4f7-cb2d51f6f1e9-activity.fit</t>
         </is>
       </c>
       <c r="AK48" t="b">
@@ -10814,7 +10820,11 @@
       </c>
       <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
       <c r="AR48" t="n">
         <v>843017438</v>
       </c>
@@ -10822,31 +10832,31 @@
         <v>1</v>
       </c>
       <c r="AT48" t="n">
-        <v>30.374771</v>
+        <v>30.37505</v>
       </c>
       <c r="AU48" t="n">
-        <v>30.508732</v>
+        <v>30.508258</v>
       </c>
       <c r="AV48" t="n">
-        <v>30.374719</v>
+        <v>30.374949</v>
       </c>
       <c r="AW48" t="n">
-        <v>30.508774</v>
+        <v>30.508911</v>
       </c>
       <c r="AX48" t="n">
-        <v>3.189</v>
+        <v>3.235</v>
       </c>
       <c r="AY48" t="n">
-        <v>35.05</v>
+        <v>34.62</v>
       </c>
       <c r="AZ48" t="n">
-        <v>39.5</v>
+        <v>37.7</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.461</v>
+        <v>5.605</v>
       </c>
       <c r="BB48" t="n">
-        <v>7.654</v>
+        <v>8.712</v>
       </c>
       <c r="BC48" s="3" t="n">
         <v>46125</v>
@@ -10885,17 +10895,225 @@
         </is>
       </c>
       <c r="BM48" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BN48" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO48" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="BP48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Outdoor walk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Walk</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Walk</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>18087447161</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46125.21821759259</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>46125.30155092593</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>(GMT+02:00) Africa/Cairo</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="b">
+        <v>0</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="X49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AA49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>19189188264</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>19189188264</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>stripped_1776059758605.fit</t>
+        </is>
+      </c>
+      <c r="AK49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="n">
+        <v>843017438</v>
+      </c>
+      <c r="AS49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>30.374771</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>30.508732</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>30.374719</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>30.508774</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>3.189</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>5.461</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>7.654</v>
+      </c>
+      <c r="BC49" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF49" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="BG49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="BI49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK49" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL49" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="BM49" t="n">
         <v>10.99</v>
       </c>
-      <c r="BN48" t="b">
-        <v>1</v>
-      </c>
-      <c r="BO48" t="inlineStr">
+      <c r="BN49" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO49" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="BP48" t="inlineStr"/>
+      <c r="BP49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
